--- a/data/wcdsc.xlsx
+++ b/data/wcdsc.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="57">
   <si>
     <t>电站名称</t>
   </si>
@@ -58,15 +58,9 @@
     <t>111号直流</t>
   </si>
   <si>
-    <t>106号直流</t>
-  </si>
-  <si>
     <t>211号直流</t>
   </si>
   <si>
-    <t>9176699400500404</t>
-  </si>
-  <si>
     <t>9176699400500305</t>
   </si>
   <si>
@@ -76,72 +70,30 @@
     <t>9176699400500604</t>
   </si>
   <si>
-    <t>303号直流</t>
-  </si>
-  <si>
     <t>109号直流</t>
   </si>
   <si>
-    <t>208号直流</t>
-  </si>
-  <si>
     <t>108号直流</t>
   </si>
   <si>
-    <t>204号直流</t>
-  </si>
-  <si>
-    <t>104号直流</t>
-  </si>
-  <si>
     <t>207号直流</t>
   </si>
   <si>
     <t>9176699355900102</t>
   </si>
   <si>
-    <t>9176699416300204</t>
-  </si>
-  <si>
-    <t>9176699425700104</t>
-  </si>
-  <si>
     <t>107号直流</t>
   </si>
   <si>
-    <t>304号直流</t>
-  </si>
-  <si>
     <t>209号直流</t>
   </si>
   <si>
-    <t>305号直流</t>
-  </si>
-  <si>
-    <t>202号直流</t>
-  </si>
-  <si>
     <t>9176699400500302</t>
   </si>
   <si>
-    <t>9176699400500403</t>
-  </si>
-  <si>
-    <t>9176699400500505</t>
-  </si>
-  <si>
     <t>9176699400500203</t>
   </si>
   <si>
-    <t>9176699400500504</t>
-  </si>
-  <si>
-    <t>9176699400500104</t>
-  </si>
-  <si>
-    <t>9176699400500202</t>
-  </si>
-  <si>
     <t>9176699400500402</t>
   </si>
   <si>
@@ -154,9 +106,6 @@
     <t>9176699400500502</t>
   </si>
   <si>
-    <t>9176699400500103</t>
-  </si>
-  <si>
     <t>9176699400500605</t>
   </si>
   <si>
@@ -166,55 +115,79 @@
     <t>9176699400500704</t>
   </si>
   <si>
-    <t>9176699355900104</t>
-  </si>
-  <si>
     <t>9176699400500702</t>
   </si>
   <si>
     <t>9176699400500705</t>
   </si>
   <si>
-    <t>9176699400500601</t>
-  </si>
-  <si>
-    <t>9176699400500602</t>
-  </si>
-  <si>
-    <t>9176699400500603</t>
-  </si>
-  <si>
-    <t>9176699400500703</t>
-  </si>
-  <si>
     <t>9176699400500701</t>
   </si>
   <si>
-    <t>9176699355900101</t>
-  </si>
-  <si>
-    <t>9176699425700301</t>
-  </si>
-  <si>
-    <t>9176699416300201</t>
-  </si>
-  <si>
     <t>9176699368200202</t>
   </si>
   <si>
-    <t>9176699420300104</t>
-  </si>
-  <si>
-    <t>9176699442100302</t>
-  </si>
-  <si>
-    <t>9176699368200405</t>
-  </si>
-  <si>
-    <t>9176699442100601</t>
-  </si>
-  <si>
-    <t>9176699368200306</t>
+    <t>9176699400501303</t>
+  </si>
+  <si>
+    <t>9176699368200406</t>
+  </si>
+  <si>
+    <t>9176699400501205</t>
+  </si>
+  <si>
+    <t>9176699400501202</t>
+  </si>
+  <si>
+    <t>9176699368200102</t>
+  </si>
+  <si>
+    <t>9176699400500401</t>
+  </si>
+  <si>
+    <t>9176699442100102</t>
+  </si>
+  <si>
+    <t>9176699400500501</t>
+  </si>
+  <si>
+    <t>9176699442100402</t>
+  </si>
+  <si>
+    <t>9176699400500105</t>
+  </si>
+  <si>
+    <t>9176699400501203</t>
+  </si>
+  <si>
+    <t>9176699368200304</t>
+  </si>
+  <si>
+    <t>302号直流</t>
+  </si>
+  <si>
+    <t>205号直流</t>
+  </si>
+  <si>
+    <t>301号直流</t>
+  </si>
+  <si>
+    <t>309号直流</t>
+  </si>
+  <si>
+    <t>110号直流</t>
+  </si>
+  <si>
+    <t>310号直流</t>
+  </si>
+  <si>
+    <t>203号直流</t>
+  </si>
+  <si>
+    <t>101号直流</t>
+  </si>
+  <si>
+    <t>103号直流</t>
   </si>
 </sst>
 </file>
@@ -651,972 +624,786 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C2" s="9">
-        <v>46075.486875000002</v>
+        <v>46086.577060185184</v>
       </c>
       <c r="D2" s="9">
-        <v>46078.258738425924</v>
-      </c>
-      <c r="E2" s="10">
-        <v>66.524722222122364</v>
-      </c>
+        <v>46089.316435185188</v>
+      </c>
+      <c r="E2" s="10"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C3" s="9">
-        <v>46077.450648148151</v>
+        <v>46087.250625000001</v>
       </c>
       <c r="D3" s="9">
-        <v>46078.258738425924</v>
-      </c>
-      <c r="E3" s="10">
-        <v>19.394166666548699</v>
-      </c>
+        <v>46089.316435185188</v>
+      </c>
+      <c r="E3" s="10"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="C4" s="9">
-        <v>46077.502372685187</v>
+        <v>46087.569826388892</v>
       </c>
       <c r="D4" s="9">
-        <v>46078.258738425924</v>
-      </c>
-      <c r="E4" s="10">
-        <v>18.1527777776937</v>
-      </c>
+        <v>46089.316435185188</v>
+      </c>
+      <c r="E4" s="10"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C5" s="9">
-        <v>46077.514513888891</v>
+        <v>46087.575219907405</v>
       </c>
       <c r="D5" s="9">
-        <v>46078.258738425924</v>
-      </c>
-      <c r="E5" s="10">
-        <v>17.861388888792135</v>
-      </c>
+        <v>46089.316435185188</v>
+      </c>
+      <c r="E5" s="10"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C6" s="9">
-        <v>46077.520266203705</v>
+        <v>46087.579444444447</v>
       </c>
       <c r="D6" s="9">
-        <v>46078.258738425924</v>
-      </c>
-      <c r="E6" s="10">
-        <v>17.723333333269693</v>
-      </c>
+        <v>46089.316435185188</v>
+      </c>
+      <c r="E6" s="10"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="C7" s="9">
-        <v>46077.523032407407</v>
+        <v>46087.665925925925</v>
       </c>
       <c r="D7" s="9">
-        <v>46078.258738425924</v>
-      </c>
-      <c r="E7" s="10">
-        <v>17.656944444403052</v>
-      </c>
+        <v>46089.316435185188</v>
+      </c>
+      <c r="E7" s="10"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C8" s="9">
-        <v>46077.523379629631</v>
+        <v>46088.02547453704</v>
       </c>
       <c r="D8" s="9">
-        <v>46078.258738425924</v>
-      </c>
-      <c r="E8" s="10">
-        <v>17.648611111042555</v>
-      </c>
+        <v>46089.316435185188</v>
+      </c>
+      <c r="E8" s="10"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C9" s="9">
-        <v>46077.527766203704</v>
+        <v>46088.065439814818</v>
       </c>
       <c r="D9" s="9">
-        <v>46078.258738425924</v>
-      </c>
-      <c r="E9" s="10">
-        <v>17.543333333276678</v>
-      </c>
+        <v>46089.316435185188</v>
+      </c>
+      <c r="E9" s="10"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A10" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C10" s="9">
-        <v>46077.57240740741</v>
+        <v>46088.123136574075</v>
       </c>
       <c r="D10" s="9">
-        <v>46078.258738425924</v>
-      </c>
-      <c r="E10" s="10">
-        <v>16.471944444347173</v>
-      </c>
+        <v>46089.316435185188</v>
+      </c>
+      <c r="E10" s="10"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C11" s="9">
-        <v>46077.596886574072</v>
+        <v>46088.201539351852</v>
       </c>
       <c r="D11" s="9">
-        <v>46078.258738425924</v>
-      </c>
-      <c r="E11" s="10">
-        <v>15.884444444440305</v>
-      </c>
+        <v>46089.316435185188</v>
+      </c>
+      <c r="E11" s="10"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A12" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C12" s="9">
-        <v>46077.616979166669</v>
+        <v>46088.343715277777</v>
       </c>
       <c r="D12" s="9">
-        <v>46078.258738425924</v>
-      </c>
-      <c r="E12" s="10">
-        <v>15.402222222124692</v>
-      </c>
+        <v>46089.316435185188</v>
+      </c>
+      <c r="E12" s="10"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A13" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C13" s="9">
-        <v>46077.631979166668</v>
+        <v>46088.362766203703</v>
       </c>
       <c r="D13" s="9">
-        <v>46078.258738425924</v>
-      </c>
-      <c r="E13" s="10">
-        <v>15.042222222138662</v>
-      </c>
+        <v>46089.316435185188</v>
+      </c>
+      <c r="E13" s="10"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A14" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C14" s="9">
-        <v>46077.635046296295</v>
+        <v>46088.468252314815</v>
       </c>
       <c r="D14" s="9">
-        <v>46078.258738425924</v>
-      </c>
-      <c r="E14" s="10">
-        <v>14.968611111107748</v>
-      </c>
+        <v>46089.316435185188</v>
+      </c>
+      <c r="E14" s="10"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A15" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="C15" s="9">
-        <v>46077.639641203707</v>
+        <v>46088.473032407404</v>
       </c>
       <c r="D15" s="9">
-        <v>46078.258738425924</v>
-      </c>
-      <c r="E15" s="10">
-        <v>14.858333333220799</v>
-      </c>
+        <v>46089.316435185188</v>
+      </c>
+      <c r="E15" s="10"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="C16" s="9">
-        <v>46077.690671296295</v>
+        <v>46088.537199074075</v>
       </c>
       <c r="D16" s="9">
-        <v>46078.258738425924</v>
-      </c>
-      <c r="E16" s="10">
-        <v>13.633611111086793</v>
-      </c>
+        <v>46089.316435185188</v>
+      </c>
+      <c r="E16" s="10"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A17" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C17" s="9">
-        <v>46077.753287037034</v>
+        <v>46088.538055555553</v>
       </c>
       <c r="D17" s="9">
-        <v>46078.258738425924</v>
-      </c>
-      <c r="E17" s="10">
-        <v>12.130833333358169</v>
-      </c>
+        <v>46089.316435185188</v>
+      </c>
+      <c r="E17" s="10"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A18" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C18" s="9">
-        <v>46067.028773148151</v>
+        <v>46088.548634259256</v>
       </c>
       <c r="D18" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E18" s="10">
-        <v>262.34472222207114</v>
-      </c>
+        <v>46089.316435185188</v>
+      </c>
+      <c r="E18" s="10"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A19" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C19" s="9">
-        <v>46067.046400462961</v>
+        <v>46088.551157407404</v>
       </c>
       <c r="D19" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E19" s="10">
-        <v>261.92166666663252</v>
-      </c>
+        <v>46089.316435185188</v>
+      </c>
+      <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A20" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C20" s="9">
-        <v>46067.410474537035</v>
+        <v>46088.558310185188</v>
       </c>
       <c r="D20" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E20" s="10">
-        <v>253.18388888885966</v>
-      </c>
+        <v>46089.316435185188</v>
+      </c>
+      <c r="E20" s="10"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A21" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C21" s="9">
-        <v>46067.4219212963</v>
+        <v>46088.567083333335</v>
       </c>
       <c r="D21" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E21" s="10">
-        <v>252.90916666650446</v>
-      </c>
+        <v>46089.316435185188</v>
+      </c>
+      <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A22" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C22" s="9">
-        <v>46067.42796296296</v>
+        <v>46088.569189814814</v>
       </c>
       <c r="D22" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E22" s="10">
-        <v>252.76416666666046</v>
-      </c>
+        <v>46089.316435185188</v>
+      </c>
+      <c r="E22" s="10"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="C23" s="9">
-        <v>46067.498310185183</v>
+        <v>46088.604618055557</v>
       </c>
       <c r="D23" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E23" s="10">
-        <v>251.07583333330695</v>
-      </c>
+        <v>46089.316435185188</v>
+      </c>
+      <c r="E23" s="10"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A24" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C24" s="9">
-        <v>46067.500115740739</v>
+        <v>46088.645428240743</v>
       </c>
       <c r="D24" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E24" s="10">
-        <v>251.03249999997206</v>
-      </c>
+        <v>46089.316435185188</v>
+      </c>
+      <c r="E24" s="10"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A25" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="C25" s="9">
-        <v>46067.515023148146</v>
+        <v>46088.648125</v>
       </c>
       <c r="D25" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E25" s="10">
-        <v>250.67472222220385</v>
-      </c>
+        <v>46089.316435185188</v>
+      </c>
+      <c r="E25" s="10"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A26" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="C26" s="9">
-        <v>46067.53638888889</v>
+        <v>46088.653946759259</v>
       </c>
       <c r="D26" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E26" s="10">
-        <v>250.1619444443495</v>
-      </c>
+        <v>46089.316435185188</v>
+      </c>
+      <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A27" s="4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C27" s="9">
-        <v>46067.5387962963</v>
+        <v>46088.663124999999</v>
       </c>
       <c r="D27" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E27" s="10">
-        <v>250.10416666651145</v>
-      </c>
+        <v>46089.316435185188</v>
+      </c>
+      <c r="E27" s="10"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A28" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C28" s="9">
-        <v>46067.540092592593</v>
+        <v>46088.708912037036</v>
       </c>
       <c r="D28" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E28" s="10">
-        <v>250.07305555546191</v>
-      </c>
+        <v>46089.316435185188</v>
+      </c>
+      <c r="E28" s="10"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A29" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C29" s="9">
-        <v>46067.543854166666</v>
+        <v>46088.712743055556</v>
       </c>
       <c r="D29" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E29" s="10">
-        <v>249.98277777771</v>
-      </c>
+        <v>46089.316435185188</v>
+      </c>
+      <c r="E29" s="10"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A30" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="C30" s="9">
-        <v>46067.545798611114</v>
+        <v>46088.7419212963</v>
       </c>
       <c r="D30" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E30" s="10">
-        <v>249.93611111096106</v>
-      </c>
+        <v>46089.316435185188</v>
+      </c>
+      <c r="E30" s="10"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A31" s="4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="C31" s="9">
-        <v>46067.556018518517</v>
+        <v>46088.782071759262</v>
       </c>
       <c r="D31" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E31" s="10">
-        <v>249.69083333329763</v>
-      </c>
+        <v>46089.316435185188</v>
+      </c>
+      <c r="E31" s="10"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A32" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C32" s="9">
-        <v>46067.566111111111</v>
+        <v>46088.807037037041</v>
       </c>
       <c r="D32" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E32" s="10">
-        <v>249.44861111103091</v>
-      </c>
+        <v>46089.316435185188</v>
+      </c>
+      <c r="E32" s="10"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A33" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C33" s="9">
-        <v>46067.56689814815</v>
+        <v>46084.583171296297</v>
       </c>
       <c r="D33" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E33" s="10">
-        <v>249.4297222220921</v>
-      </c>
+        <v>46089.300787037035</v>
+      </c>
+      <c r="E33" s="10"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A34" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="C34" s="9">
-        <v>46067.574733796297</v>
+        <v>46087.755960648145</v>
       </c>
       <c r="D34" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E34" s="10">
-        <v>249.2416666665813</v>
-      </c>
+        <v>46089.300787037035</v>
+      </c>
+      <c r="E34" s="10"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A35" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="C35" s="9">
-        <v>46067.599710648145</v>
+        <v>46088.529895833337</v>
       </c>
       <c r="D35" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E35" s="10">
-        <v>248.64222222223179</v>
-      </c>
+        <v>46089.300787037035</v>
+      </c>
+      <c r="E35" s="10"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A36" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="C36" s="9">
-        <v>46068.061053240737</v>
+        <v>46088.533599537041</v>
       </c>
       <c r="D36" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E36" s="10">
-        <v>237.57000000000698</v>
-      </c>
+        <v>46089.300787037035</v>
+      </c>
+      <c r="E36" s="10"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A37" s="11" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="C37" s="12">
-        <v>46068.157824074071</v>
+        <v>46088.535798611112</v>
       </c>
       <c r="D37" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E37" s="13">
-        <v>235.24749999999767</v>
-      </c>
+        <v>46089.300787037035</v>
+      </c>
+      <c r="E37" s="13"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A38" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="C38" s="9">
-        <v>46068.359259259261</v>
+        <v>46088.548993055556</v>
       </c>
       <c r="D38" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E38" s="10">
-        <v>230.41305555542931</v>
-      </c>
+        <v>46089.300787037035</v>
+      </c>
+      <c r="E38" s="10"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A39" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>49</v>
       </c>
       <c r="C39" s="9">
-        <v>46068.584710648145</v>
+        <v>46088.560277777775</v>
       </c>
       <c r="D39" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E39" s="10">
-        <v>225.00222222221782</v>
-      </c>
+        <v>46089.300787037035</v>
+      </c>
+      <c r="E39" s="10"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A40" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>50</v>
       </c>
       <c r="C40" s="9">
-        <v>46068.64640046296</v>
+        <v>46088.560902777775</v>
       </c>
       <c r="D40" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E40" s="10">
-        <v>223.52166666666744</v>
-      </c>
+        <v>46089.300787037035</v>
+      </c>
+      <c r="E40" s="10"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A41" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>51</v>
       </c>
       <c r="C41" s="9">
-        <v>46069.03701388889</v>
+        <v>46088.570185185185</v>
       </c>
       <c r="D41" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E41" s="10">
-        <v>214.14694444433553</v>
-      </c>
+        <v>46089.300787037035</v>
+      </c>
+      <c r="E41" s="10"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A42" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>52</v>
       </c>
       <c r="C42" s="9">
-        <v>46069.039027777777</v>
+        <v>46088.570462962962</v>
       </c>
       <c r="D42" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E42" s="10">
-        <v>214.0986111110542</v>
-      </c>
+        <v>46089.300787037035</v>
+      </c>
+      <c r="E42" s="10"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A43" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>53</v>
       </c>
       <c r="C43" s="9">
-        <v>46069.062962962962</v>
+        <v>46088.63076388889</v>
       </c>
       <c r="D43" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E43" s="10">
-        <v>213.52416666661156</v>
-      </c>
+        <v>46089.300787037035</v>
+      </c>
+      <c r="E43" s="10"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A44" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C44" s="9">
-        <v>46069.076944444445</v>
+        <v>46088.661805555559</v>
       </c>
       <c r="D44" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E44" s="10">
-        <v>213.1886111110216</v>
-      </c>
+        <v>46089.300787037035</v>
+      </c>
+      <c r="E44" s="10"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A45" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="C45" s="9">
-        <v>46069.149050925924</v>
+        <v>46088.709907407407</v>
       </c>
       <c r="D45" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E45" s="10">
-        <v>211.45805555552943</v>
-      </c>
+        <v>46089.300787037035</v>
+      </c>
+      <c r="E45" s="10"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A46" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C46" s="9">
-        <v>46069.242245370369</v>
+        <v>46088.714270833334</v>
       </c>
       <c r="D46" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E46" s="10">
-        <v>209.22138888883637</v>
-      </c>
+        <v>46089.300787037035</v>
+      </c>
+      <c r="E46" s="10"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A47" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C47" s="9">
-        <v>46069.364270833335</v>
+        <v>46088.71465277778</v>
       </c>
       <c r="D47" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E47" s="10">
-        <v>206.29277777764946</v>
-      </c>
+        <v>46089.300787037035</v>
+      </c>
+      <c r="E47" s="10"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A48" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C48" s="9">
-        <v>46072.606724537036</v>
+        <v>46088.782199074078</v>
       </c>
       <c r="D48" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E48" s="10">
-        <v>128.4738888888387</v>
-      </c>
+        <v>46089.300787037035</v>
+      </c>
+      <c r="E48" s="10"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A49" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="C49" s="9">
-        <v>46075.610694444447</v>
+        <v>46088.786064814813</v>
       </c>
       <c r="D49" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E49" s="10">
-        <v>56.378611110965721</v>
-      </c>
+        <v>46089.300787037035</v>
+      </c>
+      <c r="E49" s="10"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A50" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C50" s="9">
-        <v>46076.588599537034</v>
-      </c>
-      <c r="D50" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E50" s="10">
-        <v>32.90888888889458</v>
-      </c>
+      <c r="A50" s="4"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="10"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A51" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C51" s="9">
-        <v>46077.013159722221</v>
-      </c>
-      <c r="D51" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E51" s="10">
-        <v>22.719444444403052</v>
-      </c>
+      <c r="A51" s="4"/>
+      <c r="B51" s="4"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="10"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A52" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C52" s="9">
-        <v>46077.11314814815</v>
-      </c>
-      <c r="D52" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E52" s="5">
-        <v>20.319722222106066</v>
-      </c>
+      <c r="A52" s="4"/>
+      <c r="B52" s="4"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="5"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A53" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C53" s="9">
-        <v>46077.135104166664</v>
-      </c>
-      <c r="D53" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E53" s="5">
-        <v>19.792777777765878</v>
-      </c>
+      <c r="A53" s="4"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="5"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A54" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C54" s="9">
-        <v>46077.159062500003</v>
-      </c>
-      <c r="D54" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E54" s="5">
-        <v>19.217777777637821</v>
-      </c>
+      <c r="A54" s="4"/>
+      <c r="B54" s="4"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="5"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A55" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C55" s="9">
-        <v>46077.165092592593</v>
-      </c>
-      <c r="D55" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E55" s="5">
-        <v>19.073055555461906</v>
-      </c>
+      <c r="A55" s="4"/>
+      <c r="B55" s="4"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="5"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A56" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C56" s="9">
-        <v>46077.181307870371</v>
-      </c>
-      <c r="D56" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E56" s="5">
-        <v>18.683888888801448</v>
-      </c>
+      <c r="A56" s="4"/>
+      <c r="B56" s="4"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="5"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A57" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C57" s="9">
-        <v>46077.292870370373</v>
-      </c>
-      <c r="D57" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E57" s="5">
-        <v>16.006388888752554</v>
-      </c>
+      <c r="A57" s="4"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="5"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A58" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C58" s="9">
-        <v>46077.305428240739</v>
-      </c>
-      <c r="D58" s="9">
-        <v>46077.959803240738</v>
-      </c>
-      <c r="E58" s="5">
-        <v>15.70499999995809</v>
-      </c>
+      <c r="A58" s="4"/>
+      <c r="B58" s="4"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="5"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A59" s="4"/>

--- a/data/wcdsc.xlsx
+++ b/data/wcdsc.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="52">
   <si>
     <t>电站名称</t>
   </si>
@@ -52,42 +52,15 @@
     <t>9176699400500205</t>
   </si>
   <si>
-    <t>9176699435600102</t>
-  </si>
-  <si>
-    <t>111号直流</t>
-  </si>
-  <si>
-    <t>211号直流</t>
-  </si>
-  <si>
     <t>9176699400500305</t>
   </si>
   <si>
-    <t>105号直流</t>
-  </si>
-  <si>
     <t>9176699400500604</t>
   </si>
   <si>
-    <t>109号直流</t>
-  </si>
-  <si>
-    <t>108号直流</t>
-  </si>
-  <si>
-    <t>207号直流</t>
-  </si>
-  <si>
     <t>9176699355900102</t>
   </si>
   <si>
-    <t>107号直流</t>
-  </si>
-  <si>
-    <t>209号直流</t>
-  </si>
-  <si>
     <t>9176699400500302</t>
   </si>
   <si>
@@ -97,57 +70,21 @@
     <t>9176699400500402</t>
   </si>
   <si>
-    <t>9176699400500301</t>
-  </si>
-  <si>
     <t>9176699400500204</t>
   </si>
   <si>
     <t>9176699400500502</t>
   </si>
   <si>
-    <t>9176699400500605</t>
-  </si>
-  <si>
-    <t>9176699355900103</t>
-  </si>
-  <si>
-    <t>9176699400500704</t>
-  </si>
-  <si>
-    <t>9176699400500702</t>
-  </si>
-  <si>
-    <t>9176699400500705</t>
-  </si>
-  <si>
-    <t>9176699400500701</t>
-  </si>
-  <si>
-    <t>9176699368200202</t>
-  </si>
-  <si>
     <t>9176699400501303</t>
   </si>
   <si>
     <t>9176699368200406</t>
   </si>
   <si>
-    <t>9176699400501205</t>
-  </si>
-  <si>
     <t>9176699400501202</t>
   </si>
   <si>
-    <t>9176699368200102</t>
-  </si>
-  <si>
-    <t>9176699400500401</t>
-  </si>
-  <si>
-    <t>9176699442100102</t>
-  </si>
-  <si>
     <t>9176699400500501</t>
   </si>
   <si>
@@ -157,37 +94,85 @@
     <t>9176699400500105</t>
   </si>
   <si>
-    <t>9176699400501203</t>
-  </si>
-  <si>
     <t>9176699368200304</t>
   </si>
   <si>
     <t>302号直流</t>
   </si>
   <si>
-    <t>205号直流</t>
-  </si>
-  <si>
-    <t>301号直流</t>
-  </si>
-  <si>
-    <t>309号直流</t>
-  </si>
-  <si>
-    <t>110号直流</t>
-  </si>
-  <si>
-    <t>310号直流</t>
-  </si>
-  <si>
     <t>203号直流</t>
   </si>
   <si>
     <t>101号直流</t>
   </si>
   <si>
-    <t>103号直流</t>
+    <t>208号直流</t>
+  </si>
+  <si>
+    <t>104号直流</t>
+  </si>
+  <si>
+    <t>201号直流</t>
+  </si>
+  <si>
+    <t>9176699400500303</t>
+  </si>
+  <si>
+    <t>9176699355900104</t>
+  </si>
+  <si>
+    <t>9176699420300101</t>
+  </si>
+  <si>
+    <t>9176699400500405</t>
+  </si>
+  <si>
+    <t>9176699368200201</t>
+  </si>
+  <si>
+    <t>9176699400501204</t>
+  </si>
+  <si>
+    <t>9176699400500403</t>
+  </si>
+  <si>
+    <t>9176699400501201</t>
+  </si>
+  <si>
+    <t>9176699400501103</t>
+  </si>
+  <si>
+    <t>9176699420300104</t>
+  </si>
+  <si>
+    <t>9176699368200101</t>
+  </si>
+  <si>
+    <t>9176699442100201</t>
+  </si>
+  <si>
+    <t>9176699400501101</t>
+  </si>
+  <si>
+    <t>9176699368200404</t>
+  </si>
+  <si>
+    <t>9176699368200306</t>
+  </si>
+  <si>
+    <t>9176699442100701</t>
+  </si>
+  <si>
+    <t>9176699368200103</t>
+  </si>
+  <si>
+    <t>9176699400500103</t>
+  </si>
+  <si>
+    <t>9176699400500202</t>
+  </si>
+  <si>
+    <t>9176699400500404</t>
   </si>
 </sst>
 </file>
@@ -624,91 +609,91 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C2" s="9">
-        <v>46086.577060185184</v>
+        <v>46091.510393518518</v>
       </c>
       <c r="D2" s="9">
-        <v>46089.316435185188</v>
+        <v>46093.432511574072</v>
       </c>
       <c r="E2" s="10"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C3" s="9">
-        <v>46087.250625000001</v>
+        <v>46092.511550925927</v>
       </c>
       <c r="D3" s="9">
-        <v>46089.316435185188</v>
+        <v>46093.432511574072</v>
       </c>
       <c r="E3" s="10"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C4" s="9">
-        <v>46087.569826388892</v>
+        <v>46092.51358796296</v>
       </c>
       <c r="D4" s="9">
-        <v>46089.316435185188</v>
+        <v>46093.432511574072</v>
       </c>
       <c r="E4" s="10"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C5" s="9">
-        <v>46087.575219907405</v>
+        <v>46092.666747685187</v>
       </c>
       <c r="D5" s="9">
-        <v>46089.316435185188</v>
+        <v>46093.432511574072</v>
       </c>
       <c r="E5" s="10"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C6" s="9">
-        <v>46087.579444444447</v>
+        <v>46092.797118055554</v>
       </c>
       <c r="D6" s="9">
-        <v>46089.316435185188</v>
+        <v>46093.432511574072</v>
       </c>
       <c r="E6" s="10"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C7" s="9">
-        <v>46087.665925925925</v>
+        <v>46092.821863425925</v>
       </c>
       <c r="D7" s="9">
-        <v>46089.316435185188</v>
+        <v>46093.432511574072</v>
       </c>
       <c r="E7" s="10"/>
     </row>
@@ -717,13 +702,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C8" s="9">
-        <v>46088.02547453704</v>
+        <v>46089.503020833334</v>
       </c>
       <c r="D8" s="9">
-        <v>46089.316435185188</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E8" s="10"/>
     </row>
@@ -735,25 +720,25 @@
         <v>33</v>
       </c>
       <c r="C9" s="9">
-        <v>46088.065439814818</v>
+        <v>46090.024780092594</v>
       </c>
       <c r="D9" s="9">
-        <v>46089.316435185188</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E9" s="10"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A10" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C10" s="9">
-        <v>46088.123136574075</v>
+        <v>46091.547048611108</v>
       </c>
       <c r="D10" s="9">
-        <v>46089.316435185188</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E10" s="10"/>
     </row>
@@ -762,13 +747,13 @@
         <v>5</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="C11" s="9">
-        <v>46088.201539351852</v>
+        <v>46091.552777777775</v>
       </c>
       <c r="D11" s="9">
-        <v>46089.316435185188</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E11" s="10"/>
     </row>
@@ -777,28 +762,28 @@
         <v>5</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C12" s="9">
-        <v>46088.343715277777</v>
+        <v>46091.565324074072</v>
       </c>
       <c r="D12" s="9">
-        <v>46089.316435185188</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E12" s="10"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A13" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C13" s="9">
-        <v>46088.362766203703</v>
+        <v>46091.676863425928</v>
       </c>
       <c r="D13" s="9">
-        <v>46089.316435185188</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E13" s="10"/>
     </row>
@@ -807,13 +792,13 @@
         <v>5</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C14" s="9">
-        <v>46088.468252314815</v>
+        <v>46091.679791666669</v>
       </c>
       <c r="D14" s="9">
-        <v>46089.316435185188</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E14" s="10"/>
     </row>
@@ -822,28 +807,28 @@
         <v>5</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="C15" s="9">
-        <v>46088.473032407404</v>
+        <v>46091.686296296299</v>
       </c>
       <c r="D15" s="9">
-        <v>46089.316435185188</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E15" s="10"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C16" s="9">
-        <v>46088.537199074075</v>
+        <v>46092.045324074075</v>
       </c>
       <c r="D16" s="9">
-        <v>46089.316435185188</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E16" s="10"/>
     </row>
@@ -852,43 +837,43 @@
         <v>5</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="C17" s="9">
-        <v>46088.538055555553</v>
+        <v>46092.077789351853</v>
       </c>
       <c r="D17" s="9">
-        <v>46089.316435185188</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E17" s="10"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A18" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C18" s="9">
-        <v>46088.548634259256</v>
+        <v>46092.204444444447</v>
       </c>
       <c r="D18" s="9">
-        <v>46089.316435185188</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E18" s="10"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A19" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="C19" s="9">
-        <v>46088.551157407404</v>
+        <v>46092.237256944441</v>
       </c>
       <c r="D19" s="9">
-        <v>46089.316435185188</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E19" s="10"/>
     </row>
@@ -897,13 +882,13 @@
         <v>5</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C20" s="9">
-        <v>46088.558310185188</v>
+        <v>46092.298356481479</v>
       </c>
       <c r="D20" s="9">
-        <v>46089.316435185188</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E20" s="10"/>
     </row>
@@ -912,13 +897,13 @@
         <v>5</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C21" s="9">
-        <v>46088.567083333335</v>
+        <v>46092.522048611114</v>
       </c>
       <c r="D21" s="9">
-        <v>46089.316435185188</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E21" s="10"/>
     </row>
@@ -927,13 +912,13 @@
         <v>5</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C22" s="9">
-        <v>46088.569189814814</v>
+        <v>46092.53634259259</v>
       </c>
       <c r="D22" s="9">
-        <v>46089.316435185188</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E22" s="10"/>
     </row>
@@ -942,13 +927,13 @@
         <v>5</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="C23" s="9">
-        <v>46088.604618055557</v>
+        <v>46092.539421296293</v>
       </c>
       <c r="D23" s="9">
-        <v>46089.316435185188</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E23" s="10"/>
     </row>
@@ -957,58 +942,58 @@
         <v>5</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C24" s="9">
-        <v>46088.645428240743</v>
+        <v>46092.547407407408</v>
       </c>
       <c r="D24" s="9">
-        <v>46089.316435185188</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E24" s="10"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A25" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C25" s="9">
-        <v>46088.648125</v>
+        <v>46092.552152777775</v>
       </c>
       <c r="D25" s="9">
-        <v>46089.316435185188</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E25" s="10"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A26" s="4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C26" s="9">
-        <v>46088.653946759259</v>
+        <v>46092.554131944446</v>
       </c>
       <c r="D26" s="9">
-        <v>46089.316435185188</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A27" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C27" s="9">
-        <v>46088.663124999999</v>
+        <v>46092.557013888887</v>
       </c>
       <c r="D27" s="9">
-        <v>46089.316435185188</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E27" s="10"/>
     </row>
@@ -1017,329 +1002,289 @@
         <v>5</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C28" s="9">
-        <v>46088.708912037036</v>
+        <v>46092.561759259261</v>
       </c>
       <c r="D28" s="9">
-        <v>46089.316435185188</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E28" s="10"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A29" s="4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C29" s="9">
-        <v>46088.712743055556</v>
+        <v>46092.564062500001</v>
       </c>
       <c r="D29" s="9">
-        <v>46089.316435185188</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E29" s="10"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A30" s="4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="C30" s="9">
-        <v>46088.7419212963</v>
+        <v>46092.571921296294</v>
       </c>
       <c r="D30" s="9">
-        <v>46089.316435185188</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E30" s="10"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A31" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>47</v>
       </c>
       <c r="C31" s="9">
-        <v>46088.782071759262</v>
+        <v>46092.573946759258</v>
       </c>
       <c r="D31" s="9">
-        <v>46089.316435185188</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E31" s="10"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A32" s="4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C32" s="9">
-        <v>46088.807037037041</v>
+        <v>46092.582291666666</v>
       </c>
       <c r="D32" s="9">
-        <v>46089.316435185188</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E32" s="10"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A33" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="C33" s="9">
-        <v>46084.583171296297</v>
+        <v>46092.583298611113</v>
       </c>
       <c r="D33" s="9">
-        <v>46089.300787037035</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E33" s="10"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A34" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C34" s="9">
-        <v>46087.755960648145</v>
+        <v>46092.585347222222</v>
       </c>
       <c r="D34" s="9">
-        <v>46089.300787037035</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E34" s="10"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A35" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C35" s="9">
-        <v>46088.529895833337</v>
+        <v>46092.588159722225</v>
       </c>
       <c r="D35" s="9">
-        <v>46089.300787037035</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E35" s="10"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A36" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C36" s="9">
-        <v>46088.533599537041</v>
+        <v>46092.597534722219</v>
       </c>
       <c r="D36" s="9">
-        <v>46089.300787037035</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E36" s="10"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A37" s="11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C37" s="12">
-        <v>46088.535798611112</v>
+        <v>46092.649525462963</v>
       </c>
       <c r="D37" s="9">
-        <v>46089.300787037035</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E37" s="13"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A38" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C38" s="9">
-        <v>46088.548993055556</v>
+        <v>46092.668043981481</v>
       </c>
       <c r="D38" s="9">
-        <v>46089.300787037035</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E38" s="10"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A39" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>49</v>
       </c>
       <c r="C39" s="9">
-        <v>46088.560277777775</v>
+        <v>46092.706400462965</v>
       </c>
       <c r="D39" s="9">
-        <v>46089.300787037035</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E39" s="10"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A40" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="C40" s="9">
-        <v>46088.560902777775</v>
+        <v>46092.719699074078</v>
       </c>
       <c r="D40" s="9">
-        <v>46089.300787037035</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E40" s="10"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A41" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41" s="9">
-        <v>46088.570185185185</v>
+        <v>46092.732511574075</v>
       </c>
       <c r="D41" s="9">
-        <v>46089.300787037035</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E41" s="10"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A42" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42" s="9">
-        <v>46088.570462962962</v>
+        <v>46092.737395833334</v>
       </c>
       <c r="D42" s="9">
-        <v>46089.300787037035</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E42" s="10"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A43" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="C43" s="9">
-        <v>46088.63076388889</v>
+        <v>46092.762476851851</v>
       </c>
       <c r="D43" s="9">
-        <v>46089.300787037035</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E43" s="10"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A44" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C44" s="9">
-        <v>46088.661805555559</v>
+        <v>46092.839201388888</v>
       </c>
       <c r="D44" s="9">
-        <v>46089.300787037035</v>
+        <v>46093.438136574077</v>
       </c>
       <c r="E44" s="10"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A45" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C45" s="9">
-        <v>46088.709907407407</v>
-      </c>
-      <c r="D45" s="9">
-        <v>46089.300787037035</v>
-      </c>
+      <c r="A45" s="4"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
       <c r="E45" s="10"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A46" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C46" s="9">
-        <v>46088.714270833334</v>
-      </c>
-      <c r="D46" s="9">
-        <v>46089.300787037035</v>
-      </c>
+      <c r="A46" s="4"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
       <c r="E46" s="10"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A47" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C47" s="9">
-        <v>46088.71465277778</v>
-      </c>
-      <c r="D47" s="9">
-        <v>46089.300787037035</v>
-      </c>
+      <c r="A47" s="4"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
       <c r="E47" s="10"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A48" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C48" s="9">
-        <v>46088.782199074078</v>
-      </c>
-      <c r="D48" s="9">
-        <v>46089.300787037035</v>
-      </c>
+      <c r="A48" s="4"/>
+      <c r="B48" s="4"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
       <c r="E48" s="10"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A49" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C49" s="9">
-        <v>46088.786064814813</v>
-      </c>
-      <c r="D49" s="9">
-        <v>46089.300787037035</v>
-      </c>
+      <c r="A49" s="4"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
       <c r="E49" s="10"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.15">
